--- a/dokumen/Dokumen Report SAL Mar 2026.xlsx
+++ b/dokumen/Dokumen Report SAL Mar 2026.xlsx
@@ -231,6 +231,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -290,16 +291,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -429,362 +434,362 @@
   <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="15.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="29.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="29.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="28.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="53.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="55.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="28.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="17.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="15.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="29.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="29.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="33.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="53.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="55.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="28.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="17.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="12.24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="0" t="n">
+      <c r="C1" s="1" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <f aca="false">B2/B3</f>
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <f aca="false">C1/C4</f>
         <v>50</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="0" t="s">
+      <c r="H9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="0" t="s">
+      <c r="I9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="0" t="s">
+      <c r="J9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="0" t="s">
+      <c r="K9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L9" s="0" t="s">
+      <c r="L9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="0" t="s">
+      <c r="M9" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>46025</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>10001</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="0" t="s">
+      <c r="G10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="0" t="s">
+      <c r="H10" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>46025</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>10002</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="G11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="0" t="s">
+      <c r="H11" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>46025</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>10002</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="0" t="s">
+      <c r="G12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="0" t="s">
+      <c r="H12" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G16" s="0" t="s">
+      <c r="G16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="0" t="s">
+      <c r="H16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I16" s="0" t="s">
+      <c r="I16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J16" s="0" t="s">
+      <c r="J16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K16" s="0" t="s">
+      <c r="K16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L16" s="0" t="s">
+      <c r="L16" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>46025</v>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="3" t="n">
         <v>0.333333333333333</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="3" t="n">
         <v>0.708333333333333</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G17" s="0" t="s">
+      <c r="G17" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H17" s="0" t="s">
+      <c r="H17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I17" s="0" t="s">
+      <c r="I17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J17" s="0" t="n">
+      <c r="J17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="K17" s="0" t="n">
+      <c r="K17" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="L17" s="0" t="n">
+      <c r="L17" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="E23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G23" s="0" t="s">
+      <c r="G23" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H23" s="0" t="s">
+      <c r="H23" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I23" s="0" t="s">
+      <c r="I23" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J23" s="0" t="s">
+      <c r="J23" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="0" t="s">
+      <c r="K23" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L23" s="0" t="s">
+      <c r="L23" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="M23" s="0" t="s">
+      <c r="M23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="N23" s="0" t="s">
+      <c r="N23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="O23" s="0" t="s">
+      <c r="O23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="P23" s="0" t="s">
+      <c r="P23" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="Q23" s="0" t="s">
+      <c r="Q23" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <v>10001</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G24" s="0" t="s">
+      <c r="G24" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H24" s="0" t="s">
+      <c r="H24" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I24" s="1" t="n">
+      <c r="I24" s="2" t="n">
         <v>46025</v>
       </c>
-      <c r="J24" s="0" t="s">
+      <c r="J24" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K24" s="1" t="n">
+      <c r="K24" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="L24" s="0" t="s">
+      <c r="L24" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="M24" s="0" t="n">
+      <c r="M24" s="1" t="n">
         <v>400000</v>
       </c>
-      <c r="N24" s="0" t="n">
+      <c r="N24" s="1" t="n">
         <v>200000</v>
       </c>
-      <c r="O24" s="0" t="n">
+      <c r="O24" s="1" t="n">
         <v>200000</v>
       </c>
-      <c r="P24" s="0" t="s">
+      <c r="P24" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="Q24" s="0" t="s">
+      <c r="Q24" s="1" t="s">
         <v>64</v>
       </c>
     </row>
